--- a/output_analysis_da2_2.xlsx
+++ b/output_analysis_da2_2.xlsx
@@ -30,7 +30,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -41,6 +41,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FF4444"/>
         <bgColor rgb="00FF4444"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CCCCCC"/>
+        <bgColor rgb="00CCCCCC"/>
       </patternFill>
     </fill>
     <fill>
@@ -80,15 +86,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -454,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J80"/>
+  <dimension ref="A1:O80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -467,6 +474,11 @@
     <col width="24" customWidth="1" min="8" max="8"/>
     <col width="24" customWidth="1" min="9" max="9"/>
     <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="35" customHeight="1">
@@ -520,6 +532,31 @@
           <t>status &amp; forecast</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>min duration</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>min duration date</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>min stop cause</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>last weak group</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>dominant weak 30d</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -529,11 +566,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>90.5</v>
+        <v>88</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -564,30 +601,53 @@
           <t>CRITICAL ↘ Хурцадмал</t>
         </is>
       </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>BATTERY_VOLTAGE</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
+        </is>
+      </c>
+      <c r="O2" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>10.63.117.212</t>
+          <t>10.63.114.104</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>101.5</v>
+        <v>100</v>
       </c>
       <c r="D3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>72.41</v>
+        <v>73</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -608,34 +668,57 @@
           <t>CRITICAL ↘ Хурцадмал</t>
         </is>
       </c>
+      <c r="K3" t="n">
+        <v>21</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>BATTERY_VOLTAGE</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>10.63.45.99</t>
+          <t>10.63.96.2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>72.5</v>
+        <v>28</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>98.62</v>
+        <v>20</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>28.57</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -650,36 +733,59 @@
       <c r="J4" s="2" t="inlineStr">
         <is>
           <t>CRITICAL ↘ Хурцадмал</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>16</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>BATTERY_VOLTAGE</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10.63.96.2</t>
+          <t>10.63.117.212</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="C5" t="n">
+        <v>33</v>
+      </c>
+      <c r="D5" t="n">
         <v>28</v>
       </c>
-      <c r="D5" t="n">
-        <v>20</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>28.57</v>
+      <c r="E5" s="5" t="n">
+        <v>15.15</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -694,36 +800,59 @@
       <c r="J5" s="2" t="inlineStr">
         <is>
           <t>CRITICAL ↘ Хурцадмал</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>BATTERY_VOLTAGE</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10.63.121.226</t>
+          <t>10.61.37.45</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>180</v>
+        <v>21</v>
       </c>
       <c r="D6" t="n">
-        <v>37</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>79.44</v>
+        <v>18</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>14.29</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -738,28 +867,51 @@
       <c r="J6" s="2" t="inlineStr">
         <is>
           <t>CRITICAL ↘ Хурцадмал</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>17</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>BATTERY_VOLTAGE</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10.63.36.34</t>
+          <t>10.60.36.252</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>95.5</v>
+        <v>1.5</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>91.62</v>
+        <v>100</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -767,7 +919,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -782,36 +934,59 @@
       <c r="J7" s="2" t="inlineStr">
         <is>
           <t>CRITICAL ↘ Хурцадмал</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>BATTERY_VOLTAGE</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10.61.37.45</t>
+          <t>10.63.45.99</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>94.5</v>
+        <v>42.5</v>
       </c>
       <c r="D8" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>80.95</v>
+        <v>97.65000000000001</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -826,36 +1001,59 @@
       <c r="J8" s="2" t="inlineStr">
         <is>
           <t>CRITICAL ↘ Хурцадмал</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>2025-12-23</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>BATTERY_VOLTAGE</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10.63.114.104</t>
+          <t>10.63.89.228</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>104</v>
+        <v>32</v>
       </c>
       <c r="D9" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>74.04000000000001</v>
+        <v>84.38</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -870,36 +1068,59 @@
       <c r="J9" s="2" t="inlineStr">
         <is>
           <t>CRITICAL ↘ Хурцадмал</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>BATTERY_VOLTAGE</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10.60.29.155</t>
+          <t>10.63.121.226</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>84</v>
+        <v>180</v>
       </c>
       <c r="D10" t="n">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>84.52</v>
+        <v>79.44</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -914,40 +1135,63 @@
       <c r="J10" s="2" t="inlineStr">
         <is>
           <t>CRITICAL ↘ Хурцадмал</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>29</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>BATTERY_VOLTAGE</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10.60.36.252</t>
+          <t>10.63.135.234</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>63</v>
+        <v>24.5</v>
       </c>
       <c r="D11" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="E11" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E11" s="2" t="n">
-        <v>100</v>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>BATTERY_VOLTAGE</t>
+          <t>BATTERY_CAPACITY</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -958,80 +1202,126 @@
       <c r="J11" s="2" t="inlineStr">
         <is>
           <t>CRITICAL ↘ Хурцадмал</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>24</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>BATTERY_CAPACITY</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10.63.135.234</t>
+          <t>10.60.21.220</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2025-05-25</t>
         </is>
       </c>
       <c r="C12" t="n">
+        <v>104</v>
+      </c>
+      <c r="D12" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>70.67</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>26</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>BATTERY_VOLTAGE</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>critical</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>CRITICAL ↘ Хурцадмал</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
         <v>25</v>
       </c>
-      <c r="D12" t="n">
-        <v>25</v>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>24</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>BATTERY_CAPACITY</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>critical</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>CRITICAL ↘ Хурцадмал</t>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>BATTERY_VOLTAGE</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10.60.21.220</t>
+          <t>10.60.20.212</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>114</v>
+        <v>22.5</v>
       </c>
       <c r="D13" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>73.25</v>
+        <v>13</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>42.22</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1046,28 +1336,51 @@
       <c r="J13" s="2" t="inlineStr">
         <is>
           <t>CRITICAL ↘ Хурцадмал</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>7</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>BATTERY_VOLTAGE</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10.60.20.212</t>
+          <t>10.63.36.34</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>120</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>89.17</v>
+        <v>85.19</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1075,7 +1388,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1090,36 +1403,59 @@
       <c r="J14" s="2" t="inlineStr">
         <is>
           <t>CRITICAL ↘ Хурцадмал</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>BATTERY_VOLTAGE</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10.63.89.228</t>
+          <t>10.63.113.34</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>43</v>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>93.51000000000001</v>
+        <v>24.5</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>43.02</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1134,28 +1470,51 @@
       <c r="J15" s="2" t="inlineStr">
         <is>
           <t>CRITICAL ↘ Хурцадмал</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>21</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>BATTERY_VOLTAGE</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10.63.113.34</t>
+          <t>10.63.171.147</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>120</v>
+        <v>52.5</v>
       </c>
       <c r="D16" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>79.58</v>
+        <v>47</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>10.48</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1163,43 +1522,66 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>BATTERY_VOLTAGE</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>critical</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>CRITICAL ↘ Хурцадмал</t>
+          <t>BATTERY_CAPACITY</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>degrading</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>AVERAGE ↗ Хэвийн</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>33</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>BATTERY_CAPACITY</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10.63.171.147</t>
+          <t>10.63.171.131</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>74</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>47</v>
-      </c>
-      <c r="E17" s="3" t="n">
-        <v>36.49</v>
+        <v>0</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>100</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1207,131 +1589,200 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>BATTERY_CAPACITY</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
+          <t>BATTERY_VOLTAGE</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
         <is>
           <t>degrading</t>
         </is>
       </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>AVERAGE ↗ Хэвийн</t>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>AVERAGE ↘ Аль хэдийн CRITICAL орчимд байна (2026-03-17)</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>BATTERY_VOLTAGE</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10.63.171.131</t>
+          <t>10.63.135.18</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>97.5</v>
+        <v>49</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>100</v>
+        <v>35</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>28.57</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>BATTERY_VOLTAGE</t>
         </is>
       </c>
-      <c r="I18" s="3" t="inlineStr">
+      <c r="I18" s="4" t="inlineStr">
         <is>
           <t>degrading</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>CRITICAL ↘ Хурцадмал</t>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>AVERAGE → Хэвийн</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>29</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>BATTERY_VOLTAGE</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10.63.135.18</t>
+          <t>10.63.48.235</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>57.5</v>
+        <v>55.5</v>
       </c>
       <c r="D19" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>40</v>
+        <v>48</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>13.51</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>BATTERY_VOLTAGE</t>
         </is>
       </c>
-      <c r="I19" s="3" t="inlineStr">
+      <c r="I19" s="4" t="inlineStr">
         <is>
           <t>degrading</t>
         </is>
       </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>AVERAGE → CRITICAL (2026-06-02)</t>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>AVERAGE → Хэвийн</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>32</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>BATTERY_VOLTAGE</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>10.63.135.26</t>
+          <t>10.63.67.3</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>180</v>
+        <v>59</v>
       </c>
       <c r="D20" t="n">
-        <v>65</v>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>63.89</v>
+        <v>55</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>6.78</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1339,43 +1790,66 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>BATTERY_VOLTAGE</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
+          <t>BATTERY_CAPACITY</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
         <is>
           <t>degrading</t>
         </is>
       </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>AVERAGE ↘ CRITICAL (2026-04-13)</t>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>AVERAGE → Хэвийн</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>50</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>BATTERY_CAPACITY</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>10.63.43.114</t>
+          <t>10.63.38.34</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>111</v>
+        <v>69.5</v>
       </c>
       <c r="D21" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>77.93000000000001</v>
+        <v>48</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>30.94</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1383,197 +1857,312 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>BATTERY_VOLTAGE</t>
         </is>
       </c>
-      <c r="I21" s="3" t="inlineStr">
+      <c r="I21" s="4" t="inlineStr">
         <is>
           <t>degrading</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>AVERAGE ↘ Аль хэдийн CRITICAL орчимд байна</t>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>AVERAGE → Хэвийн</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>35</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>BATTERY_VOLTAGE</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>10.63.48.235</t>
+          <t>10.63.43.114</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2023-10-08</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>209</v>
+        <v>45</v>
       </c>
       <c r="D22" t="n">
-        <v>48</v>
-      </c>
-      <c r="E22" s="2" t="n">
-        <v>77.03</v>
+        <v>24.5</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>45.56</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>BATTERY_VOLTAGE</t>
         </is>
       </c>
-      <c r="I22" s="3" t="inlineStr">
+      <c r="I22" s="4" t="inlineStr">
         <is>
           <t>degrading</t>
         </is>
       </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>AVERAGE ↗ Хэвийн</t>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>AVERAGE ↘ Аль хэдийн CRITICAL орчимд байна (2026-03-17)</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>21</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>BATTERY_VOLTAGE</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>10.63.67.3</t>
+          <t>10.61.98.60</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2023-10-10</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="D23" t="n">
-        <v>55</v>
-      </c>
-      <c r="E23" s="3" t="n">
-        <v>32.1</v>
+        <v>49</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>BATTERY_CAPACITY</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="inlineStr">
+          <t>BATTERY_VOLTAGE</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
         <is>
           <t>degrading</t>
         </is>
       </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>AVERAGE → Хэвийн</t>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>AVERAGE ↘ CRITICAL (2026-03-22)</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>43</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>BATTERY_VOLTAGE</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
+        </is>
+      </c>
+      <c r="O23" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>10.63.33.146</t>
+          <t>10.63.135.26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>76</v>
+        <v>180</v>
       </c>
       <c r="D24" t="n">
-        <v>46</v>
-      </c>
-      <c r="E24" s="3" t="n">
-        <v>39.47</v>
+        <v>65</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>63.89</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>BATTERY_VOLTAGE</t>
         </is>
       </c>
-      <c r="I24" s="3" t="inlineStr">
+      <c r="I24" s="4" t="inlineStr">
         <is>
           <t>degrading</t>
         </is>
       </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>AVERAGE ↗ Хэвийн</t>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>AVERAGE ↘ CRITICAL (2026-04-14)</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>57</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>BATTERY_VOLTAGE</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>10.61.49.45</t>
+          <t>10.63.33.146</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="D25" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="E25" s="4" t="n">
-        <v>13.93</v>
+        <v>46</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>4.17</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>BATTERY_VOLTAGE</t>
         </is>
       </c>
-      <c r="I25" s="3" t="inlineStr">
+      <c r="I25" s="4" t="inlineStr">
         <is>
           <t>degrading</t>
         </is>
       </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>AVERAGE → CRITICAL (2026-10-08)</t>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>AVERAGE → Хэвийн</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>26</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>BATTERY_VOLTAGE</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
         </is>
       </c>
     </row>
@@ -1585,105 +2174,151 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>47.5</v>
+        <v>46.5</v>
       </c>
       <c r="D26" t="n">
         <v>40</v>
       </c>
-      <c r="E26" s="4" t="n">
-        <v>15.79</v>
+      <c r="E26" s="5" t="n">
+        <v>13.98</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>BATTERY_VOLTAGE</t>
         </is>
       </c>
-      <c r="I26" s="3" t="inlineStr">
+      <c r="I26" s="4" t="inlineStr">
         <is>
           <t>degrading</t>
         </is>
       </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>AVERAGE → CRITICAL (2027-02-16)</t>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>AVERAGE → Хэвийн</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>25</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>BATTERY_VOLTAGE</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>10.63.93.98</t>
+          <t>10.60.29.155</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>89.5</v>
+        <v>48.5</v>
       </c>
       <c r="D27" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>67.59999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>BATTERY_VOLTAGE</t>
         </is>
       </c>
-      <c r="I27" s="3" t="inlineStr">
+      <c r="I27" s="4" t="inlineStr">
         <is>
           <t>degrading</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>AVERAGE ↘ Аль хэдийн CRITICAL орчимд байна</t>
+          <t>AVERAGE ↘ Аль хэдийн CRITICAL орчимд байна (2026-03-17)</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>BATTERY_VOLTAGE</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>10.63.38.34</t>
+          <t>10.63.93.98</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>69.5</v>
+        <v>76.5</v>
       </c>
       <c r="D28" t="n">
-        <v>48</v>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>30.94</v>
+        <v>29</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>62.09</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1691,21 +2326,44 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>BATTERY_VOLTAGE</t>
         </is>
       </c>
-      <c r="I28" s="3" t="inlineStr">
+      <c r="I28" s="4" t="inlineStr">
         <is>
           <t>degrading</t>
         </is>
       </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>AVERAGE → Хэвийн</t>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>AVERAGE ↘ Аль хэдийн CRITICAL орчимд байна (2026-03-18)</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>16</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>BATTERY_VOLTAGE</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
         </is>
       </c>
     </row>
@@ -1742,14 +2400,37 @@
           <t>BATTERY_VOLTAGE</t>
         </is>
       </c>
-      <c r="I29" s="3" t="inlineStr">
+      <c r="I29" s="4" t="inlineStr">
         <is>
           <t>degrading</t>
         </is>
       </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>AVERAGE ↘ CRITICAL (2026-06-14)</t>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>AVERAGE ↘ CRITICAL (2026-06-15)</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>39</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>2024-09-15</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>BATTERY_VOLTAGE</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
         </is>
       </c>
     </row>
@@ -1761,17 +2442,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>74</v>
+        <v>47</v>
       </c>
       <c r="D30" t="n">
         <v>24</v>
       </c>
-      <c r="E30" s="2" t="n">
-        <v>67.56999999999999</v>
+      <c r="E30" s="4" t="n">
+        <v>48.94</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1786,65 +2467,111 @@
           <t>BATTERY_VOLTAGE</t>
         </is>
       </c>
-      <c r="I30" s="3" t="inlineStr">
+      <c r="I30" s="4" t="inlineStr">
         <is>
           <t>degrading</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>CRITICAL ↘ Хурцадмал</t>
+          <t>AVERAGE ↘ Аль хэдийн CRITICAL орчимд байна (2026-03-18)</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>21</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>BATTERY_VOLTAGE</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
+        </is>
+      </c>
+      <c r="O30" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10.61.98.60</t>
+          <t>10.63.45.146</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>51.5</v>
+        <v>180</v>
       </c>
       <c r="D31" t="n">
-        <v>51.5</v>
-      </c>
-      <c r="E31" s="4" t="n">
+        <v>180</v>
+      </c>
+      <c r="E31" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>43</v>
+        <v>180</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>BATTERY_VOLTAGE</t>
-        </is>
-      </c>
-      <c r="I31" s="3" t="inlineStr">
-        <is>
-          <t>degrading</t>
-        </is>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>AVERAGE ↘ CRITICAL (2026-03-14)</t>
+          <t>MAX_TIME</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>stable</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>VERY GOOD → Өгөгдөл хүрэлцэхгүй</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>180</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>MAX_TIME</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
+        </is>
+      </c>
+      <c r="O31" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10.63.6.139</t>
+          <t>10.63.43.90</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1853,13 +2580,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>103</v>
+        <v>71</v>
       </c>
       <c r="D32" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>67.95999999999999</v>
+        <v>71.83</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1867,33 +2594,56 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>BATTERY_VOLTAGE</t>
-        </is>
-      </c>
-      <c r="I32" s="4" t="inlineStr">
+          <t>BATTERY_CAPACITY</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
         <is>
           <t>stable</t>
         </is>
       </c>
-      <c r="J32" s="5" t="inlineStr">
-        <is>
-          <t>GOOD ↘ AVERAGE (2026-03-19)</t>
+      <c r="J32" s="6" t="inlineStr">
+        <is>
+          <t>GOOD → AVERAGE (2026-08-20)</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>68</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>BATTERY_CAPACITY</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>10.63.45.146</t>
+          <t>10.63.43.50</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1902,12 +2652,12 @@
       <c r="D33" t="n">
         <v>180</v>
       </c>
-      <c r="E33" s="4" t="n">
+      <c r="E33" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -1918,466 +2668,719 @@
           <t>MAX_TIME</t>
         </is>
       </c>
-      <c r="I33" s="4" t="inlineStr">
+      <c r="I33" s="5" t="inlineStr">
         <is>
           <t>stable</t>
         </is>
       </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>VERY GOOD → Өгөгдөл хүрэлцэхгүй</t>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>VERY GOOD → Хэвийн</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>171</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>BATTERY_VOLTAGE</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10.63.51.50</t>
+          <t>10.63.46.226</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>480</v>
+        <v>180</v>
       </c>
       <c r="D34" t="n">
-        <v>480</v>
-      </c>
-      <c r="E34" s="4" t="n">
+        <v>180</v>
+      </c>
+      <c r="E34" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>480</v>
+        <v>180</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
           <t>MAX_TIME</t>
         </is>
       </c>
-      <c r="I34" s="4" t="inlineStr">
+      <c r="I34" s="5" t="inlineStr">
         <is>
           <t>stable</t>
         </is>
       </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>VERY GOOD → Өгөгдөл хүрэлцэхгүй</t>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>VERY GOOD → Хэвийн</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>180</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>MAX_TIME</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10.63.43.90</t>
+          <t>10.63.51.50</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>71</v>
+        <v>480</v>
       </c>
       <c r="D35" t="n">
-        <v>20</v>
-      </c>
-      <c r="E35" s="2" t="n">
-        <v>71.83</v>
+        <v>480</v>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>70</v>
+        <v>480</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>BATTERY_CAPACITY</t>
-        </is>
-      </c>
-      <c r="I35" s="4" t="inlineStr">
+          <t>MAX_TIME</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
         <is>
           <t>stable</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>GOOD → AVERAGE (2026-08-19)</t>
+          <t>VERY GOOD → Хэвийн</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>480</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>MAX_TIME</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>10.63.46.226</t>
+          <t>10.60.20.132</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="D36" t="n">
-        <v>180</v>
-      </c>
-      <c r="E36" s="4" t="n">
-        <v>0</v>
+        <v>108.5</v>
+      </c>
+      <c r="E36" s="5" t="n">
+        <v>9.58</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>180</v>
+        <v>113</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>MAX_TIME</t>
-        </is>
-      </c>
-      <c r="I36" s="4" t="inlineStr">
+          <t>BATTERY_CAPACITY</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
         <is>
           <t>stable</t>
         </is>
       </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>VERY GOOD → Хэвийн</t>
+      <c r="J36" s="6" t="inlineStr">
+        <is>
+          <t>GOOD → Хэвийн</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>97</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>BATTERY_VOLTAGE</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>10.60.20.132</t>
+          <t>10.63.63.235</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="C37" t="n">
+        <v>177</v>
+      </c>
+      <c r="D37" t="n">
+        <v>150</v>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>128</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>BATTERY_VOLTAGE</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>stable</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>VERY GOOD ↘ GOOD (2026-03-13)</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
         <v>120</v>
       </c>
-      <c r="D37" t="n">
-        <v>107</v>
-      </c>
-      <c r="E37" s="4" t="n">
-        <v>10.83</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G37" t="n">
-        <v>112</v>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>BATTERY_CAPACITY</t>
-        </is>
-      </c>
-      <c r="I37" s="4" t="inlineStr">
-        <is>
-          <t>stable</t>
-        </is>
-      </c>
-      <c r="J37" s="5" t="inlineStr">
-        <is>
-          <t>GOOD → Хэвийн</t>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>BATTERY_VOLTAGE</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
+        </is>
+      </c>
+      <c r="O37" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>10.63.63.235</t>
+          <t>10.63.63.26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="D38" t="n">
-        <v>150</v>
-      </c>
-      <c r="E38" s="4" t="n">
-        <v>15.25</v>
+        <v>180</v>
+      </c>
+      <c r="E38" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>128</v>
+        <v>180</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>BATTERY_VOLTAGE</t>
-        </is>
-      </c>
-      <c r="I38" s="4" t="inlineStr">
+          <t>MAX_TIME</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
         <is>
           <t>stable</t>
         </is>
       </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>VERY GOOD ↘ GOOD (2026-03-12)</t>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>VERY GOOD → Хэвийн</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
+        <v>180</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>MAX_TIME</t>
+        </is>
+      </c>
+      <c r="N38" s="4" t="inlineStr">
+        <is>
+          <t>group1</t>
+        </is>
+      </c>
+      <c r="O38" s="4" t="inlineStr">
+        <is>
+          <t>group1</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>10.63.63.26</t>
+          <t>10.63.64.226</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>180</v>
+        <v>85.5</v>
       </c>
       <c r="D39" t="n">
-        <v>180</v>
-      </c>
-      <c r="E39" s="4" t="n">
-        <v>0</v>
+        <v>70.5</v>
+      </c>
+      <c r="E39" s="5" t="n">
+        <v>17.54</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>180</v>
+        <v>72</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>MAX_TIME</t>
-        </is>
-      </c>
-      <c r="I39" s="4" t="inlineStr">
+          <t>BATTERY_VOLTAGE</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
         <is>
           <t>stable</t>
         </is>
       </c>
-      <c r="J39" s="4" t="inlineStr">
-        <is>
-          <t>VERY GOOD → Хэвийн</t>
+      <c r="J39" s="6" t="inlineStr">
+        <is>
+          <t>GOOD → AVERAGE (2026-07-24)</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
+        <v>46</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>BATTERY_VOLTAGE</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
+        </is>
+      </c>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>10.63.64.226</t>
+          <t>10.63.66.98</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>116</v>
+        <v>180</v>
       </c>
       <c r="D40" t="n">
-        <v>70.5</v>
-      </c>
-      <c r="E40" s="3" t="n">
-        <v>39.22</v>
+        <v>87</v>
+      </c>
+      <c r="E40" s="4" t="n">
+        <v>51.67</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2025-03-01</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>BATTERY_VOLTAGE</t>
         </is>
       </c>
-      <c r="I40" s="4" t="inlineStr">
+      <c r="I40" s="5" t="inlineStr">
         <is>
           <t>stable</t>
         </is>
       </c>
-      <c r="J40" s="5" t="inlineStr">
-        <is>
-          <t>GOOD → AVERAGE (2026-07-23)</t>
+      <c r="J40" s="6" t="inlineStr">
+        <is>
+          <t>GOOD → Хэвийн</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>81</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>BATTERY_VOLTAGE</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
+        </is>
+      </c>
+      <c r="O40" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>10.63.66.98</t>
+          <t>10.63.67.46</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="C41" t="n">
         <v>180</v>
       </c>
       <c r="D41" t="n">
-        <v>87</v>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>51.67</v>
+        <v>180</v>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2025-03-01</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>85</v>
+        <v>180</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>BATTERY_VOLTAGE</t>
-        </is>
-      </c>
-      <c r="I41" s="4" t="inlineStr">
+          <t>MAX_TIME</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
         <is>
           <t>stable</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>GOOD → Хэвийн</t>
+          <t>VERY GOOD → Хэвийн</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
+        <v>180</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>MAX_TIME</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>10.63.67.40</t>
+          <t>10.63.69.228</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>89</v>
+        <v>120</v>
       </c>
       <c r="D42" t="n">
-        <v>85.5</v>
-      </c>
-      <c r="E42" s="4" t="n">
-        <v>3.93</v>
+        <v>100</v>
+      </c>
+      <c r="E42" s="5" t="n">
+        <v>16.67</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>91</v>
+        <v>131</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
           <t>BATTERY_CAPACITY</t>
         </is>
       </c>
-      <c r="I42" s="4" t="inlineStr">
+      <c r="I42" s="5" t="inlineStr">
         <is>
           <t>stable</t>
         </is>
       </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
-          <t>GOOD ↗ Хэвийн</t>
+          <t>VERY GOOD ↗ Хэвийн</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>67</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>BATTERY_VOLTAGE</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
+        </is>
+      </c>
+      <c r="O42" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>10.63.67.46</t>
+          <t>10.63.6.139</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>180</v>
+        <v>103</v>
       </c>
       <c r="D43" t="n">
-        <v>180</v>
-      </c>
-      <c r="E43" s="4" t="n">
-        <v>0</v>
+        <v>33</v>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>67.95999999999999</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>180</v>
+        <v>91</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>MAX_TIME</t>
-        </is>
-      </c>
-      <c r="I43" s="4" t="inlineStr">
+          <t>BATTERY_VOLTAGE</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
         <is>
           <t>stable</t>
         </is>
       </c>
-      <c r="J43" s="4" t="inlineStr">
-        <is>
-          <t>VERY GOOD → Хэвийн</t>
+      <c r="J43" s="6" t="inlineStr">
+        <is>
+          <t>GOOD ↘ AVERAGE (2026-03-20)</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
+        <v>91</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>BATTERY_VOLTAGE</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
+        </is>
+      </c>
+      <c r="O43" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>10.63.69.228</t>
+          <t>10.63.70.132</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2025-02-09</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -2386,96 +3389,142 @@
       <c r="D44" t="n">
         <v>100</v>
       </c>
-      <c r="E44" s="3" t="n">
+      <c r="E44" s="4" t="n">
         <v>37.3</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>BATTERY_CAPACITY</t>
-        </is>
-      </c>
-      <c r="I44" s="4" t="inlineStr">
+          <t>BATTERY_VOLTAGE</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
         <is>
           <t>stable</t>
         </is>
       </c>
-      <c r="J44" s="5" t="inlineStr">
+      <c r="J44" s="6" t="inlineStr">
         <is>
           <t>GOOD → Хэвийн</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
+        <v>90</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>BATTERY_VOLTAGE</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
+        </is>
+      </c>
+      <c r="O44" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>10.63.70.132</t>
+          <t>10.63.73.131</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>184</v>
+        <v>117.5</v>
       </c>
       <c r="D45" t="n">
-        <v>100</v>
-      </c>
-      <c r="E45" s="3" t="n">
-        <v>45.65</v>
+        <v>113</v>
+      </c>
+      <c r="E45" s="5" t="n">
+        <v>3.83</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>BATTERY_VOLTAGE</t>
-        </is>
-      </c>
-      <c r="I45" s="4" t="inlineStr">
+          <t>BATTERY_CAPACITY</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
         <is>
           <t>stable</t>
         </is>
       </c>
-      <c r="J45" s="5" t="inlineStr">
+      <c r="J45" s="6" t="inlineStr">
         <is>
           <t>GOOD → Хэвийн</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>BATTERY_VOLTAGE</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>10.63.73.131</t>
+          <t>10.63.89.195</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>132.5</v>
+        <v>120</v>
       </c>
       <c r="D46" t="n">
-        <v>113</v>
-      </c>
-      <c r="E46" s="4" t="n">
-        <v>14.72</v>
+        <v>100</v>
+      </c>
+      <c r="E46" s="5" t="n">
+        <v>16.67</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -2483,43 +3532,66 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>BATTERY_CAPACITY</t>
-        </is>
-      </c>
-      <c r="I46" s="4" t="inlineStr">
+          <t>BATTERY_VOLTAGE</t>
+        </is>
+      </c>
+      <c r="I46" s="5" t="inlineStr">
         <is>
           <t>stable</t>
         </is>
       </c>
-      <c r="J46" s="5" t="inlineStr">
-        <is>
-          <t>GOOD → Хэвийн</t>
+      <c r="J46" s="6" t="inlineStr">
+        <is>
+          <t>GOOD ↗ Хэвийн</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
+        <v>57</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>BATTERY_VOLTAGE</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>10.63.89.195</t>
+          <t>10.63.93.58</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2024-12-12</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="C47" t="n">
         <v>120</v>
       </c>
       <c r="D47" t="n">
-        <v>100</v>
-      </c>
-      <c r="E47" s="4" t="n">
-        <v>16.67</v>
+        <v>120</v>
+      </c>
+      <c r="E47" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -2527,77 +3599,123 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>BATTERY_VOLTAGE</t>
-        </is>
-      </c>
-      <c r="I47" s="4" t="inlineStr">
+          <t>MAX_TIME</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr">
         <is>
           <t>stable</t>
         </is>
       </c>
-      <c r="J47" s="5" t="inlineStr">
-        <is>
-          <t>GOOD ↗ Хэвийн</t>
+      <c r="J47" s="6" t="inlineStr">
+        <is>
+          <t>GOOD → Хэвийн</t>
+        </is>
+      </c>
+      <c r="K47" t="n">
+        <v>91</v>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>BATTERY_VOLTAGE</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>equal</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>10.63.93.58</t>
+          <t>10.63.94.162</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="D48" t="n">
-        <v>120</v>
-      </c>
-      <c r="E48" s="4" t="n">
+        <v>180</v>
+      </c>
+      <c r="E48" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
           <t>MAX_TIME</t>
         </is>
       </c>
-      <c r="I48" s="4" t="inlineStr">
+      <c r="I48" s="5" t="inlineStr">
         <is>
           <t>stable</t>
         </is>
       </c>
       <c r="J48" s="5" t="inlineStr">
         <is>
-          <t>GOOD → Хэвийн</t>
+          <t>VERY GOOD → Хэвийн</t>
+        </is>
+      </c>
+      <c r="K48" t="n">
+        <v>180</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>MAX_TIME</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
+        </is>
+      </c>
+      <c r="O48" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>10.63.94.162</t>
+          <t>10.63.63.10</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2025-05-24</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -2606,12 +3724,12 @@
       <c r="D49" t="n">
         <v>180</v>
       </c>
-      <c r="E49" s="4" t="n">
+      <c r="E49" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -2622,36 +3740,59 @@
           <t>MAX_TIME</t>
         </is>
       </c>
-      <c r="I49" s="4" t="inlineStr">
+      <c r="I49" s="5" t="inlineStr">
         <is>
           <t>stable</t>
         </is>
       </c>
-      <c r="J49" s="4" t="inlineStr">
+      <c r="J49" s="5" t="inlineStr">
         <is>
           <t>VERY GOOD → Хэвийн</t>
+        </is>
+      </c>
+      <c r="K49" t="n">
+        <v>180</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>MAX_TIME</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
+        </is>
+      </c>
+      <c r="O49" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>10.63.63.10</t>
+          <t>10.63.67.40</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>180</v>
+        <v>89</v>
       </c>
       <c r="D50" t="n">
-        <v>180</v>
-      </c>
-      <c r="E50" s="4" t="n">
-        <v>0</v>
+        <v>85.5</v>
+      </c>
+      <c r="E50" s="5" t="n">
+        <v>3.93</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -2659,33 +3800,56 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>180</v>
+        <v>91</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>MAX_TIME</t>
-        </is>
-      </c>
-      <c r="I50" s="4" t="inlineStr">
+          <t>BATTERY_CAPACITY</t>
+        </is>
+      </c>
+      <c r="I50" s="5" t="inlineStr">
         <is>
           <t>stable</t>
         </is>
       </c>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t>VERY GOOD → Хэвийн</t>
+      <c r="J50" s="6" t="inlineStr">
+        <is>
+          <t>GOOD ↗ Хэвийн</t>
+        </is>
+      </c>
+      <c r="K50" t="n">
+        <v>71</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>BATTERY_VOLTAGE</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
+        </is>
+      </c>
+      <c r="O50" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>10.63.43.50</t>
+          <t>10.63.19.98</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -2694,7 +3858,7 @@
       <c r="D51" t="n">
         <v>180</v>
       </c>
-      <c r="E51" s="4" t="n">
+      <c r="E51" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F51" t="inlineStr">
@@ -2710,36 +3874,59 @@
           <t>MAX_TIME</t>
         </is>
       </c>
-      <c r="I51" s="4" t="inlineStr">
+      <c r="I51" s="5" t="inlineStr">
         <is>
           <t>stable</t>
         </is>
       </c>
-      <c r="J51" s="4" t="inlineStr">
-        <is>
-          <t>VERY GOOD → Хэвийн</t>
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t>VERY GOOD ↗ Хэвийн</t>
+        </is>
+      </c>
+      <c r="K51" t="n">
+        <v>171</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>BATTERY_VOLTAGE</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
+        </is>
+      </c>
+      <c r="O51" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>10.63.19.98</t>
+          <t>10.63.37.50</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>180</v>
+        <v>57</v>
       </c>
       <c r="D52" t="n">
-        <v>180</v>
-      </c>
-      <c r="E52" s="4" t="n">
-        <v>0</v>
+        <v>22.5</v>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>60.53</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -2747,43 +3934,66 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>180</v>
+        <v>64</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>MAX_TIME</t>
-        </is>
-      </c>
-      <c r="I52" s="4" t="inlineStr">
+          <t>BATTERY_CAPACITY</t>
+        </is>
+      </c>
+      <c r="I52" s="5" t="inlineStr">
         <is>
           <t>stable</t>
         </is>
       </c>
-      <c r="J52" s="4" t="inlineStr">
-        <is>
-          <t>VERY GOOD ↗ Хэвийн</t>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>GOOD ↘ Аль хэдийн CRITICAL орчимд байна (2026-03-17)</t>
+        </is>
+      </c>
+      <c r="K52" t="n">
+        <v>3</v>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>BATTERY_VOLTAGE</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
+        </is>
+      </c>
+      <c r="O52" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>10.63.37.50</t>
+          <t>10.60.27.116</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2024-03-12</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="D53" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="E53" s="2" t="n">
-        <v>71.88</v>
+        <v>120</v>
+      </c>
+      <c r="E53" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -2791,33 +4001,56 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>64</v>
+        <v>120</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
+          <t>MAX_TIME</t>
+        </is>
+      </c>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>stable</t>
+        </is>
+      </c>
+      <c r="J53" s="6" t="inlineStr">
+        <is>
+          <t>GOOD → Хэвийн</t>
+        </is>
+      </c>
+      <c r="K53" t="n">
+        <v>106</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
           <t>BATTERY_CAPACITY</t>
         </is>
       </c>
-      <c r="I53" s="4" t="inlineStr">
-        <is>
-          <t>stable</t>
-        </is>
-      </c>
-      <c r="J53" s="5" t="inlineStr">
-        <is>
-          <t>GOOD ↗ Хэвийн</t>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
+        </is>
+      </c>
+      <c r="O53" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>10.60.27.116</t>
+          <t>10.60.27.252</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -2826,12 +4059,12 @@
       <c r="D54" t="n">
         <v>120</v>
       </c>
-      <c r="E54" s="4" t="n">
+      <c r="E54" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -2842,124 +4075,193 @@
           <t>MAX_TIME</t>
         </is>
       </c>
-      <c r="I54" s="4" t="inlineStr">
+      <c r="I54" s="5" t="inlineStr">
         <is>
           <t>stable</t>
         </is>
       </c>
-      <c r="J54" s="5" t="inlineStr">
+      <c r="J54" s="6" t="inlineStr">
         <is>
           <t>GOOD → Хэвийн</t>
+        </is>
+      </c>
+      <c r="K54" t="n">
+        <v>120</v>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>MAX_TIME</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
+        </is>
+      </c>
+      <c r="O54" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>10.60.27.252</t>
+          <t>10.60.28.19</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="D55" t="n">
-        <v>120</v>
+        <v>62.5</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>0</v>
+        <v>43.69</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>MAX_TIME</t>
-        </is>
-      </c>
-      <c r="I55" s="4" t="inlineStr">
+          <t>BATTERY_CAPACITY</t>
+        </is>
+      </c>
+      <c r="I55" s="5" t="inlineStr">
         <is>
           <t>stable</t>
         </is>
       </c>
-      <c r="J55" s="5" t="inlineStr">
-        <is>
-          <t>GOOD → Хэвийн</t>
+      <c r="J55" s="6" t="inlineStr">
+        <is>
+          <t>GOOD ↗ Хэвийн</t>
+        </is>
+      </c>
+      <c r="K55" t="n">
+        <v>103</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>BATTERY_CAPACITY</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
+        </is>
+      </c>
+      <c r="O55" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>10.60.28.19</t>
+          <t>10.60.29.108</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>107</v>
+        <v>240</v>
       </c>
       <c r="D56" t="n">
-        <v>58.5</v>
-      </c>
-      <c r="E56" s="3" t="n">
-        <v>45.33</v>
+        <v>240</v>
+      </c>
+      <c r="E56" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>112</v>
+        <v>240</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>BATTERY_CAPACITY</t>
-        </is>
-      </c>
-      <c r="I56" s="4" t="inlineStr">
+          <t>MAX_TIME</t>
+        </is>
+      </c>
+      <c r="I56" s="5" t="inlineStr">
         <is>
           <t>stable</t>
         </is>
       </c>
       <c r="J56" s="5" t="inlineStr">
         <is>
-          <t>GOOD ↗ Хэвийн</t>
+          <t>VERY GOOD → Хэвийн</t>
+        </is>
+      </c>
+      <c r="K56" t="n">
+        <v>240</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>MAX_TIME</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
+        </is>
+      </c>
+      <c r="O56" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>10.60.29.108</t>
+          <t>10.60.29.116</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>240</v>
+        <v>120</v>
       </c>
       <c r="D57" t="n">
-        <v>240</v>
-      </c>
-      <c r="E57" s="4" t="n">
-        <v>0</v>
+        <v>109.5</v>
+      </c>
+      <c r="E57" s="5" t="n">
+        <v>8.75</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -2967,197 +4269,312 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>240</v>
+        <v>115</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>MAX_TIME</t>
-        </is>
-      </c>
-      <c r="I57" s="4" t="inlineStr">
+          <t>BATTERY_CAPACITY</t>
+        </is>
+      </c>
+      <c r="I57" s="5" t="inlineStr">
         <is>
           <t>stable</t>
         </is>
       </c>
-      <c r="J57" s="4" t="inlineStr">
-        <is>
-          <t>VERY GOOD → Хэвийн</t>
+      <c r="J57" s="6" t="inlineStr">
+        <is>
+          <t>GOOD → Хэвийн</t>
+        </is>
+      </c>
+      <c r="K57" t="n">
+        <v>98</v>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>2026-01-03</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>BATTERY_CAPACITY</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
+        </is>
+      </c>
+      <c r="O57" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>10.60.29.116</t>
+          <t>10.61.48.44</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="D58" t="n">
-        <v>109.5</v>
-      </c>
-      <c r="E58" s="4" t="n">
-        <v>8.75</v>
+        <v>45</v>
+      </c>
+      <c r="E58" s="2" t="n">
+        <v>70</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>115</v>
+        <v>159</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
           <t>BATTERY_CAPACITY</t>
         </is>
       </c>
-      <c r="I58" s="4" t="inlineStr">
+      <c r="I58" s="5" t="inlineStr">
         <is>
           <t>stable</t>
         </is>
       </c>
       <c r="J58" s="5" t="inlineStr">
         <is>
-          <t>GOOD → Хэвийн</t>
+          <t>VERY GOOD ↗ Хэвийн</t>
+        </is>
+      </c>
+      <c r="K58" t="n">
+        <v>145</v>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>BATTERY_CAPACITY</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
+        </is>
+      </c>
+      <c r="O58" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>10.61.48.44</t>
+          <t>10.61.49.180</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>150</v>
+        <v>133.5</v>
       </c>
       <c r="D59" t="n">
-        <v>45</v>
-      </c>
-      <c r="E59" s="2" t="n">
-        <v>70</v>
+        <v>89</v>
+      </c>
+      <c r="E59" s="4" t="n">
+        <v>33.33</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>159</v>
+        <v>98</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>BATTERY_CAPACITY</t>
-        </is>
-      </c>
-      <c r="I59" s="4" t="inlineStr">
+          <t>BATTERY_VOLTAGE</t>
+        </is>
+      </c>
+      <c r="I59" s="5" t="inlineStr">
         <is>
           <t>stable</t>
         </is>
       </c>
-      <c r="J59" s="4" t="inlineStr">
-        <is>
-          <t>VERY GOOD ↗ Хэвийн</t>
+      <c r="J59" s="6" t="inlineStr">
+        <is>
+          <t>GOOD → Хэвийн</t>
+        </is>
+      </c>
+      <c r="K59" t="n">
+        <v>76</v>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>BATTERY_VOLTAGE</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
+        </is>
+      </c>
+      <c r="O59" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>10.61.49.180</t>
+          <t>10.61.49.4</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>143</v>
+        <v>131.5</v>
       </c>
       <c r="D60" t="n">
-        <v>89</v>
-      </c>
-      <c r="E60" s="3" t="n">
-        <v>37.76</v>
+        <v>120</v>
+      </c>
+      <c r="E60" s="5" t="n">
+        <v>8.75</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>98</v>
+        <v>145</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
           <t>BATTERY_VOLTAGE</t>
         </is>
       </c>
-      <c r="I60" s="4" t="inlineStr">
+      <c r="I60" s="5" t="inlineStr">
         <is>
           <t>stable</t>
         </is>
       </c>
       <c r="J60" s="5" t="inlineStr">
         <is>
-          <t>GOOD → Хэвийн</t>
+          <t>VERY GOOD ↗ Хэвийн</t>
+        </is>
+      </c>
+      <c r="K60" t="n">
+        <v>107</v>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>BATTERY_VOLTAGE</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
+        </is>
+      </c>
+      <c r="O60" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>10.61.49.4</t>
+          <t>10.61.49.45</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>129.5</v>
+        <v>62.5</v>
       </c>
       <c r="D61" t="n">
-        <v>120</v>
-      </c>
-      <c r="E61" s="4" t="n">
-        <v>7.34</v>
+        <v>52.5</v>
+      </c>
+      <c r="E61" s="5" t="n">
+        <v>16</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>135</v>
+        <v>65</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
           <t>BATTERY_VOLTAGE</t>
         </is>
       </c>
-      <c r="I61" s="4" t="inlineStr">
+      <c r="I61" s="5" t="inlineStr">
         <is>
           <t>stable</t>
         </is>
       </c>
-      <c r="J61" s="4" t="inlineStr">
-        <is>
-          <t>VERY GOOD ↗ Хэвийн</t>
+      <c r="J61" s="6" t="inlineStr">
+        <is>
+          <t>GOOD ↗ Хэвийн</t>
+        </is>
+      </c>
+      <c r="K61" t="n">
+        <v>46</v>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>BATTERY_VOLTAGE</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
+        </is>
+      </c>
+      <c r="O61" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
         </is>
       </c>
     </row>
@@ -3169,17 +4586,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="D62" t="n">
         <v>79</v>
       </c>
-      <c r="E62" s="3" t="n">
-        <v>50.93</v>
+      <c r="E62" s="4" t="n">
+        <v>49.68</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -3194,14 +4611,37 @@
           <t>BATTERY_VOLTAGE</t>
         </is>
       </c>
-      <c r="I62" s="4" t="inlineStr">
+      <c r="I62" s="5" t="inlineStr">
         <is>
           <t>stable</t>
         </is>
       </c>
-      <c r="J62" s="5" t="inlineStr">
+      <c r="J62" s="6" t="inlineStr">
         <is>
           <t>GOOD ↗ Хэвийн</t>
+        </is>
+      </c>
+      <c r="K62" t="n">
+        <v>56</v>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>BATTERY_VOLTAGE</t>
+        </is>
+      </c>
+      <c r="N62" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
+        </is>
+      </c>
+      <c r="O62" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
         </is>
       </c>
     </row>
@@ -3217,35 +4657,58 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>106.5</v>
+        <v>106</v>
       </c>
       <c r="D63" t="n">
-        <v>106.5</v>
-      </c>
-      <c r="E63" s="4" t="n">
+        <v>106</v>
+      </c>
+      <c r="E63" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
           <t>BATTERY_CAPACITY</t>
         </is>
       </c>
-      <c r="I63" s="4" t="inlineStr">
+      <c r="I63" s="5" t="inlineStr">
         <is>
           <t>stable</t>
         </is>
       </c>
-      <c r="J63" s="5" t="inlineStr">
-        <is>
-          <t>GOOD ↘ AVERAGE (2026-04-02)</t>
+      <c r="J63" s="6" t="inlineStr">
+        <is>
+          <t>GOOD ↘ AVERAGE (2026-04-01)</t>
+        </is>
+      </c>
+      <c r="K63" t="n">
+        <v>99</v>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>BATTERY_CAPACITY</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
+        </is>
+      </c>
+      <c r="O63" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
         </is>
       </c>
     </row>
@@ -3266,12 +4729,12 @@
       <c r="D64" t="n">
         <v>180</v>
       </c>
-      <c r="E64" s="4" t="n">
+      <c r="E64" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -3282,40 +4745,63 @@
           <t>MAX_TIME</t>
         </is>
       </c>
-      <c r="I64" s="4" t="inlineStr">
+      <c r="I64" s="5" t="inlineStr">
         <is>
           <t>stable</t>
         </is>
       </c>
-      <c r="J64" s="4" t="inlineStr">
+      <c r="J64" s="5" t="inlineStr">
         <is>
           <t>VERY GOOD → Хэвийн</t>
+        </is>
+      </c>
+      <c r="K64" t="n">
+        <v>180</v>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>MAX_TIME</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
+        </is>
+      </c>
+      <c r="O64" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>10.63.114.130</t>
+          <t>10.63.43.123</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="C65" t="n">
         <v>180</v>
       </c>
       <c r="D65" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>0</v>
+        <v>33.33</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -3326,26 +4812,49 @@
           <t>MAX_TIME</t>
         </is>
       </c>
-      <c r="I65" s="4" t="inlineStr">
+      <c r="I65" s="5" t="inlineStr">
         <is>
           <t>stable</t>
         </is>
       </c>
-      <c r="J65" s="4" t="inlineStr">
+      <c r="J65" s="5" t="inlineStr">
         <is>
           <t>VERY GOOD → Хэвийн</t>
+        </is>
+      </c>
+      <c r="K65" t="n">
+        <v>180</v>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>MAX_TIME</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
+        </is>
+      </c>
+      <c r="O65" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>10.63.120.8</t>
+          <t>10.63.114.130</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -3354,12 +4863,12 @@
       <c r="D66" t="n">
         <v>180</v>
       </c>
-      <c r="E66" s="4" t="n">
+      <c r="E66" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -3370,14 +4879,37 @@
           <t>MAX_TIME</t>
         </is>
       </c>
-      <c r="I66" s="4" t="inlineStr">
+      <c r="I66" s="5" t="inlineStr">
         <is>
           <t>stable</t>
         </is>
       </c>
-      <c r="J66" s="4" t="inlineStr">
-        <is>
-          <t>VERY GOOD ↘ GOOD (2027-01-27)</t>
+      <c r="J66" s="5" t="inlineStr">
+        <is>
+          <t>VERY GOOD → Хэвийн</t>
+        </is>
+      </c>
+      <c r="K66" t="n">
+        <v>180</v>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>MAX_TIME</t>
+        </is>
+      </c>
+      <c r="N66" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
+        </is>
+      </c>
+      <c r="O66" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
         </is>
       </c>
     </row>
@@ -3398,12 +4930,12 @@
       <c r="D67" t="n">
         <v>180</v>
       </c>
-      <c r="E67" s="4" t="n">
+      <c r="E67" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -3414,14 +4946,37 @@
           <t>MAX_TIME</t>
         </is>
       </c>
-      <c r="I67" s="4" t="inlineStr">
+      <c r="I67" s="5" t="inlineStr">
         <is>
           <t>stable</t>
         </is>
       </c>
-      <c r="J67" s="4" t="inlineStr">
+      <c r="J67" s="5" t="inlineStr">
         <is>
           <t>VERY GOOD → Хэвийн</t>
+        </is>
+      </c>
+      <c r="K67" t="n">
+        <v>180</v>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>MAX_TIME</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
+        </is>
+      </c>
+      <c r="O67" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
         </is>
       </c>
     </row>
@@ -3442,12 +4997,12 @@
       <c r="D68" t="n">
         <v>180</v>
       </c>
-      <c r="E68" s="4" t="n">
+      <c r="E68" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -3458,14 +5013,37 @@
           <t>MAX_TIME</t>
         </is>
       </c>
-      <c r="I68" s="4" t="inlineStr">
+      <c r="I68" s="5" t="inlineStr">
         <is>
           <t>stable</t>
         </is>
       </c>
-      <c r="J68" s="4" t="inlineStr">
+      <c r="J68" s="5" t="inlineStr">
         <is>
           <t>VERY GOOD → Хэвийн</t>
+        </is>
+      </c>
+      <c r="K68" t="n">
+        <v>180</v>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>MAX_TIME</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
+        </is>
+      </c>
+      <c r="O68" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
         </is>
       </c>
     </row>
@@ -3486,12 +5064,12 @@
       <c r="D69" t="n">
         <v>180</v>
       </c>
-      <c r="E69" s="4" t="n">
+      <c r="E69" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -3502,14 +5080,37 @@
           <t>MAX_TIME</t>
         </is>
       </c>
-      <c r="I69" s="4" t="inlineStr">
+      <c r="I69" s="5" t="inlineStr">
         <is>
           <t>stable</t>
         </is>
       </c>
-      <c r="J69" s="4" t="inlineStr">
+      <c r="J69" s="5" t="inlineStr">
         <is>
           <t>VERY GOOD → Хэвийн</t>
+        </is>
+      </c>
+      <c r="K69" t="n">
+        <v>180</v>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>MAX_TIME</t>
+        </is>
+      </c>
+      <c r="N69" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
+        </is>
+      </c>
+      <c r="O69" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
         </is>
       </c>
     </row>
@@ -3530,12 +5131,12 @@
       <c r="D70" t="n">
         <v>180</v>
       </c>
-      <c r="E70" s="4" t="n">
+      <c r="E70" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -3546,14 +5147,37 @@
           <t>MAX_TIME</t>
         </is>
       </c>
-      <c r="I70" s="4" t="inlineStr">
+      <c r="I70" s="5" t="inlineStr">
         <is>
           <t>stable</t>
         </is>
       </c>
-      <c r="J70" s="4" t="inlineStr">
+      <c r="J70" s="5" t="inlineStr">
         <is>
           <t>VERY GOOD → Хэвийн</t>
+        </is>
+      </c>
+      <c r="K70" t="n">
+        <v>180</v>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>MAX_TIME</t>
+        </is>
+      </c>
+      <c r="N70" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
+        </is>
+      </c>
+      <c r="O70" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
         </is>
       </c>
     </row>
@@ -3574,12 +5198,12 @@
       <c r="D71" t="n">
         <v>180</v>
       </c>
-      <c r="E71" s="4" t="n">
+      <c r="E71" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -3590,14 +5214,37 @@
           <t>MAX_TIME</t>
         </is>
       </c>
-      <c r="I71" s="4" t="inlineStr">
+      <c r="I71" s="5" t="inlineStr">
         <is>
           <t>stable</t>
         </is>
       </c>
-      <c r="J71" s="4" t="inlineStr">
+      <c r="J71" s="5" t="inlineStr">
         <is>
           <t>VERY GOOD → Хэвийн</t>
+        </is>
+      </c>
+      <c r="K71" t="n">
+        <v>180</v>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>MAX_TIME</t>
+        </is>
+      </c>
+      <c r="N71" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
+        </is>
+      </c>
+      <c r="O71" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
         </is>
       </c>
     </row>
@@ -3618,12 +5265,12 @@
       <c r="D72" t="n">
         <v>180</v>
       </c>
-      <c r="E72" s="4" t="n">
+      <c r="E72" s="5" t="n">
         <v>13.67</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -3634,14 +5281,37 @@
           <t>MAX_TIME</t>
         </is>
       </c>
-      <c r="I72" s="4" t="inlineStr">
+      <c r="I72" s="5" t="inlineStr">
         <is>
           <t>stable</t>
         </is>
       </c>
-      <c r="J72" s="4" t="inlineStr">
-        <is>
-          <t>VERY GOOD ↘ GOOD (2026-06-29)</t>
+      <c r="J72" s="5" t="inlineStr">
+        <is>
+          <t>VERY GOOD ↘ GOOD (2026-07-26)</t>
+        </is>
+      </c>
+      <c r="K72" t="n">
+        <v>151</v>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>BATTERY_CAPACITY</t>
+        </is>
+      </c>
+      <c r="N72" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
+        </is>
+      </c>
+      <c r="O72" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
         </is>
       </c>
     </row>
@@ -3653,17 +5323,17 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>120</v>
+        <v>108.5</v>
       </c>
       <c r="D73" t="n">
         <v>101.5</v>
       </c>
-      <c r="E73" s="4" t="n">
-        <v>15.42</v>
+      <c r="E73" s="5" t="n">
+        <v>6.45</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -3678,14 +5348,37 @@
           <t>BATTERY_CAPACITY</t>
         </is>
       </c>
-      <c r="I73" s="4" t="inlineStr">
+      <c r="I73" s="5" t="inlineStr">
         <is>
           <t>stable</t>
         </is>
       </c>
-      <c r="J73" s="5" t="inlineStr">
+      <c r="J73" s="6" t="inlineStr">
         <is>
           <t>GOOD → Хэвийн</t>
+        </is>
+      </c>
+      <c r="K73" t="n">
+        <v>81</v>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>BATTERY_VOLTAGE</t>
+        </is>
+      </c>
+      <c r="N73" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
+        </is>
+      </c>
+      <c r="O73" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
         </is>
       </c>
     </row>
@@ -3706,12 +5399,12 @@
       <c r="D74" t="n">
         <v>180</v>
       </c>
-      <c r="E74" s="4" t="n">
+      <c r="E74" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -3722,14 +5415,37 @@
           <t>MAX_TIME</t>
         </is>
       </c>
-      <c r="I74" s="4" t="inlineStr">
+      <c r="I74" s="5" t="inlineStr">
         <is>
           <t>stable</t>
         </is>
       </c>
-      <c r="J74" s="4" t="inlineStr">
+      <c r="J74" s="5" t="inlineStr">
         <is>
           <t>VERY GOOD → Хэвийн</t>
+        </is>
+      </c>
+      <c r="K74" t="n">
+        <v>180</v>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>MAX_TIME</t>
+        </is>
+      </c>
+      <c r="N74" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
+        </is>
+      </c>
+      <c r="O74" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
         </is>
       </c>
     </row>
@@ -3750,7 +5466,7 @@
       <c r="D75" t="n">
         <v>53</v>
       </c>
-      <c r="E75" s="4" t="n">
+      <c r="E75" s="5" t="n">
         <v>15.87</v>
       </c>
       <c r="F75" t="inlineStr">
@@ -3766,14 +5482,37 @@
           <t>BATTERY_CAPACITY</t>
         </is>
       </c>
-      <c r="I75" s="4" t="inlineStr">
+      <c r="I75" s="5" t="inlineStr">
         <is>
           <t>stable</t>
         </is>
       </c>
-      <c r="J75" s="5" t="inlineStr">
+      <c r="J75" s="6" t="inlineStr">
         <is>
           <t>GOOD → Хэвийн</t>
+        </is>
+      </c>
+      <c r="K75" t="n">
+        <v>48</v>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>BATTERY_CAPACITY</t>
+        </is>
+      </c>
+      <c r="N75" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
+        </is>
+      </c>
+      <c r="O75" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
         </is>
       </c>
     </row>
@@ -3785,39 +5524,62 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>180</v>
+        <v>176.5</v>
       </c>
       <c r="D76" t="n">
         <v>121</v>
       </c>
-      <c r="E76" s="3" t="n">
-        <v>32.78</v>
+      <c r="E76" s="4" t="n">
+        <v>31.44</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G76" t="n">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
           <t>BATTERY_VOLTAGE</t>
         </is>
       </c>
-      <c r="I76" s="4" t="inlineStr">
+      <c r="I76" s="5" t="inlineStr">
         <is>
           <t>stable</t>
         </is>
       </c>
-      <c r="J76" s="4" t="inlineStr">
-        <is>
-          <t>VERY GOOD ↗ Хэвийн</t>
+      <c r="J76" s="6" t="inlineStr">
+        <is>
+          <t>GOOD → Хэвийн</t>
+        </is>
+      </c>
+      <c r="K76" t="n">
+        <v>57</v>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>BATTERY_VOLTAGE</t>
+        </is>
+      </c>
+      <c r="N76" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
+        </is>
+      </c>
+      <c r="O76" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
         </is>
       </c>
     </row>
@@ -3838,12 +5600,12 @@
       <c r="D77" t="n">
         <v>180</v>
       </c>
-      <c r="E77" s="4" t="n">
+      <c r="E77" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -3854,14 +5616,37 @@
           <t>MAX_TIME</t>
         </is>
       </c>
-      <c r="I77" s="4" t="inlineStr">
+      <c r="I77" s="5" t="inlineStr">
         <is>
           <t>stable</t>
         </is>
       </c>
-      <c r="J77" s="4" t="inlineStr">
+      <c r="J77" s="5" t="inlineStr">
         <is>
           <t>VERY GOOD → Өгөгдөл хүрэлцэхгүй</t>
+        </is>
+      </c>
+      <c r="K77" t="n">
+        <v>180</v>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>MAX_TIME</t>
+        </is>
+      </c>
+      <c r="N77" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
+        </is>
+      </c>
+      <c r="O77" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
         </is>
       </c>
     </row>
@@ -3882,7 +5667,7 @@
       <c r="D78" t="n">
         <v>96</v>
       </c>
-      <c r="E78" s="4" t="n">
+      <c r="E78" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F78" t="inlineStr">
@@ -3898,40 +5683,63 @@
           <t>BATTERY_CAPACITY</t>
         </is>
       </c>
-      <c r="I78" s="4" t="inlineStr">
+      <c r="I78" s="5" t="inlineStr">
         <is>
           <t>stable</t>
         </is>
       </c>
-      <c r="J78" s="5" t="inlineStr">
-        <is>
-          <t>GOOD ↘ AVERAGE (2026-04-28)</t>
+      <c r="J78" s="6" t="inlineStr">
+        <is>
+          <t>GOOD ↘ AVERAGE (2026-04-29)</t>
+        </is>
+      </c>
+      <c r="K78" t="n">
+        <v>94</v>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>BATTERY_CAPACITY</t>
+        </is>
+      </c>
+      <c r="N78" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
+        </is>
+      </c>
+      <c r="O78" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>10.63.43.123</t>
+          <t>10.63.120.8</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="C79" t="n">
         <v>180</v>
       </c>
       <c r="D79" t="n">
-        <v>120</v>
-      </c>
-      <c r="E79" s="3" t="n">
-        <v>33.33</v>
+        <v>180</v>
+      </c>
+      <c r="E79" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -3942,14 +5750,37 @@
           <t>MAX_TIME</t>
         </is>
       </c>
-      <c r="I79" s="4" t="inlineStr">
+      <c r="I79" s="5" t="inlineStr">
         <is>
           <t>stable</t>
         </is>
       </c>
-      <c r="J79" s="4" t="inlineStr">
-        <is>
-          <t>VERY GOOD → Хэвийн</t>
+      <c r="J79" s="5" t="inlineStr">
+        <is>
+          <t>VERY GOOD ↘ 1 жилд буурахгүй</t>
+        </is>
+      </c>
+      <c r="K79" t="n">
+        <v>180</v>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>MAX_TIME</t>
+        </is>
+      </c>
+      <c r="N79" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
+        </is>
+      </c>
+      <c r="O79" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
         </is>
       </c>
     </row>
@@ -3970,12 +5801,12 @@
       <c r="D80" t="n">
         <v>180</v>
       </c>
-      <c r="E80" s="4" t="n">
+      <c r="E80" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -3986,14 +5817,37 @@
           <t>MAX_TIME</t>
         </is>
       </c>
-      <c r="I80" s="4" t="inlineStr">
+      <c r="I80" s="5" t="inlineStr">
         <is>
           <t>stable</t>
         </is>
       </c>
-      <c r="J80" s="4" t="inlineStr">
+      <c r="J80" s="5" t="inlineStr">
         <is>
           <t>VERY GOOD → Хэвийн</t>
+        </is>
+      </c>
+      <c r="K80" t="n">
+        <v>180</v>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>MAX_TIME</t>
+        </is>
+      </c>
+      <c r="N80" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
+        </is>
+      </c>
+      <c r="O80" s="3" t="inlineStr">
+        <is>
+          <t>single_group1</t>
         </is>
       </c>
     </row>
